--- a/处理数据/excel/新质生产力测度指标/工业机器人安装密度.xlsx
+++ b/处理数据/excel/新质生产力测度指标/工业机器人安装密度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tjjmlinxieli\处理数据\excel\新质生产力测度指标\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BE5C175-8D75-4940-B0BE-EA5E374D5F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E321D52-06F2-4784-A998-E4746BD88DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="15196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="35">
   <si>
     <t>年份</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>云南</t>
-  </si>
-  <si>
-    <t>西藏</t>
   </si>
   <si>
     <t>陕西</t>
@@ -521,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="15.59765625" customWidth="1"/>
@@ -539,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -4028,7 +4025,7 @@
         <v>450000</v>
       </c>
       <c r="D195" s="2">
-        <f t="shared" ref="D195:D258" si="3">B195+C195</f>
+        <f t="shared" ref="D195:D251" si="3">B195+C195</f>
         <v>452017</v>
       </c>
       <c r="E195" s="2">
@@ -5049,13 +5046,15 @@
         <v>2014</v>
       </c>
       <c r="C252" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D252" s="2">
-        <f t="shared" si="3"/>
-        <v>542014</v>
-      </c>
-      <c r="E252" s="2"/>
+        <f t="shared" ref="D252:D301" si="4">B252+C252</f>
+        <v>612014</v>
+      </c>
+      <c r="E252" s="2">
+        <v>3824.367361539948</v>
+      </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
@@ -5065,13 +5064,15 @@
         <v>2015</v>
       </c>
       <c r="C253" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D253" s="2">
-        <f t="shared" si="3"/>
-        <v>542015</v>
-      </c>
-      <c r="E253" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612015</v>
+      </c>
+      <c r="E253" s="2">
+        <v>5225.95</v>
+      </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
@@ -5081,13 +5082,15 @@
         <v>2016</v>
       </c>
       <c r="C254" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D254" s="2">
-        <f t="shared" si="3"/>
-        <v>542016</v>
-      </c>
-      <c r="E254" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612016</v>
+      </c>
+      <c r="E254" s="2">
+        <v>7093.0990000000002</v>
+      </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
@@ -5097,13 +5100,15 @@
         <v>2017</v>
       </c>
       <c r="C255" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D255" s="2">
-        <f t="shared" si="3"/>
-        <v>542017</v>
-      </c>
-      <c r="E255" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612017</v>
+      </c>
+      <c r="E255" s="2">
+        <v>9815.6790000000001</v>
+      </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
@@ -5113,13 +5118,15 @@
         <v>2018</v>
       </c>
       <c r="C256" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D256" s="2">
-        <f t="shared" si="3"/>
-        <v>542018</v>
-      </c>
-      <c r="E256" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612018</v>
+      </c>
+      <c r="E256" s="2">
+        <v>12169.81</v>
+      </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
@@ -5129,13 +5136,15 @@
         <v>2019</v>
       </c>
       <c r="C257" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D257" s="2">
-        <f t="shared" si="3"/>
-        <v>542019</v>
-      </c>
-      <c r="E257" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612019</v>
+      </c>
+      <c r="E257" s="2">
+        <v>13408.26</v>
+      </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
@@ -5145,13 +5154,15 @@
         <v>2020</v>
       </c>
       <c r="C258" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D258" s="2">
-        <f t="shared" si="3"/>
-        <v>542020</v>
-      </c>
-      <c r="E258" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612020</v>
+      </c>
+      <c r="E258" s="2">
+        <v>14929.9</v>
+      </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
@@ -5161,13 +5172,15 @@
         <v>2021</v>
       </c>
       <c r="C259" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D259" s="2">
-        <f t="shared" ref="D259:D311" si="4">B259+C259</f>
-        <v>542021</v>
-      </c>
-      <c r="E259" s="2"/>
+        <f t="shared" si="4"/>
+        <v>612021</v>
+      </c>
+      <c r="E259" s="2">
+        <v>16688.63</v>
+      </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
@@ -5177,13 +5190,15 @@
         <v>2022</v>
       </c>
       <c r="C260" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D260" s="2">
         <f t="shared" si="4"/>
-        <v>542022</v>
-      </c>
-      <c r="E260" s="2"/>
+        <v>612022</v>
+      </c>
+      <c r="E260" s="2">
+        <v>18447.36</v>
+      </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
@@ -5193,13 +5208,15 @@
         <v>2023</v>
       </c>
       <c r="C261" s="2">
-        <v>540000</v>
+        <v>610000</v>
       </c>
       <c r="D261" s="2">
         <f t="shared" si="4"/>
-        <v>542023</v>
-      </c>
-      <c r="E261" s="2"/>
+        <v>612023</v>
+      </c>
+      <c r="E261" s="2">
+        <v>20391.439999999999</v>
+      </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
@@ -5209,14 +5226,14 @@
         <v>2014</v>
       </c>
       <c r="C262" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D262" s="2">
         <f t="shared" si="4"/>
-        <v>612014</v>
+        <v>622014</v>
       </c>
       <c r="E262" s="2">
-        <v>3824.367361539948</v>
+        <v>488.58089257616678</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
@@ -5227,14 +5244,14 @@
         <v>2015</v>
       </c>
       <c r="C263" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D263" s="2">
         <f t="shared" si="4"/>
-        <v>612015</v>
+        <v>622015</v>
       </c>
       <c r="E263" s="2">
-        <v>5225.95</v>
+        <v>716.88229999999999</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
@@ -5245,14 +5262,14 @@
         <v>2016</v>
       </c>
       <c r="C264" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D264" s="2">
         <f t="shared" si="4"/>
-        <v>612016</v>
+        <v>622016</v>
       </c>
       <c r="E264" s="2">
-        <v>7093.0990000000002</v>
+        <v>937.55470000000003</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
@@ -5263,14 +5280,14 @@
         <v>2017</v>
       </c>
       <c r="C265" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D265" s="2">
         <f t="shared" si="4"/>
-        <v>612017</v>
+        <v>622017</v>
       </c>
       <c r="E265" s="2">
-        <v>9815.6790000000001</v>
+        <v>1289.789</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
@@ -5281,14 +5298,14 @@
         <v>2018</v>
       </c>
       <c r="C266" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D266" s="2">
         <f t="shared" si="4"/>
-        <v>612018</v>
+        <v>622018</v>
       </c>
       <c r="E266" s="2">
-        <v>12169.81</v>
+        <v>1675.1</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
@@ -5299,14 +5316,14 @@
         <v>2019</v>
       </c>
       <c r="C267" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D267" s="2">
         <f t="shared" si="4"/>
-        <v>612019</v>
+        <v>622019</v>
       </c>
       <c r="E267" s="2">
-        <v>13408.26</v>
+        <v>2402.6959999999999</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
@@ -5317,14 +5334,14 @@
         <v>2020</v>
       </c>
       <c r="C268" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D268" s="2">
         <f t="shared" si="4"/>
-        <v>612020</v>
+        <v>622020</v>
       </c>
       <c r="E268" s="2">
-        <v>14929.9</v>
+        <v>2298.2539999999999</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
@@ -5335,14 +5352,14 @@
         <v>2021</v>
       </c>
       <c r="C269" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D269" s="2">
         <f t="shared" si="4"/>
-        <v>612021</v>
+        <v>622021</v>
       </c>
       <c r="E269" s="2">
-        <v>16688.63</v>
+        <v>2581.3020000000001</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
@@ -5353,14 +5370,14 @@
         <v>2022</v>
       </c>
       <c r="C270" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D270" s="2">
         <f t="shared" si="4"/>
-        <v>612022</v>
+        <v>622022</v>
       </c>
       <c r="E270" s="2">
-        <v>18447.36</v>
+        <v>2864.348</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
@@ -5371,14 +5388,14 @@
         <v>2023</v>
       </c>
       <c r="C271" s="2">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="D271" s="2">
         <f t="shared" si="4"/>
-        <v>612023</v>
+        <v>622023</v>
       </c>
       <c r="E271" s="2">
-        <v>20391.439999999999</v>
+        <v>3178.43</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
@@ -5389,14 +5406,14 @@
         <v>2014</v>
       </c>
       <c r="C272" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D272" s="2">
         <f t="shared" si="4"/>
-        <v>622014</v>
+        <v>632014</v>
       </c>
       <c r="E272" s="2">
-        <v>488.58089257616678</v>
+        <v>185.9736249081414</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
@@ -5407,14 +5424,14 @@
         <v>2015</v>
       </c>
       <c r="C273" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D273" s="2">
         <f t="shared" si="4"/>
-        <v>622015</v>
+        <v>632015</v>
       </c>
       <c r="E273" s="2">
-        <v>716.88229999999999</v>
+        <v>263.70749999999998</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
@@ -5425,14 +5442,14 @@
         <v>2016</v>
       </c>
       <c r="C274" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D274" s="2">
         <f t="shared" si="4"/>
-        <v>622016</v>
+        <v>632016</v>
       </c>
       <c r="E274" s="2">
-        <v>937.55470000000003</v>
+        <v>346.1474</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
@@ -5443,14 +5460,14 @@
         <v>2017</v>
       </c>
       <c r="C275" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D275" s="2">
         <f t="shared" si="4"/>
-        <v>622017</v>
+        <v>632017</v>
       </c>
       <c r="E275" s="2">
-        <v>1289.789</v>
+        <v>470.05500000000001</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
@@ -5461,14 +5478,14 @@
         <v>2018</v>
       </c>
       <c r="C276" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D276" s="2">
         <f t="shared" si="4"/>
-        <v>622018</v>
+        <v>632018</v>
       </c>
       <c r="E276" s="2">
-        <v>1675.1</v>
+        <v>549.56590000000006</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
@@ -5479,14 +5496,14 @@
         <v>2019</v>
       </c>
       <c r="C277" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D277" s="2">
         <f t="shared" si="4"/>
-        <v>622019</v>
+        <v>632019</v>
       </c>
       <c r="E277" s="2">
-        <v>2402.6959999999999</v>
+        <v>714.80079999999998</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
@@ -5497,14 +5514,14 @@
         <v>2020</v>
       </c>
       <c r="C278" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D278" s="2">
         <f t="shared" si="4"/>
-        <v>622020</v>
+        <v>632020</v>
       </c>
       <c r="E278" s="2">
-        <v>2298.2539999999999</v>
+        <v>730.4991</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
@@ -5515,14 +5532,14 @@
         <v>2021</v>
       </c>
       <c r="C279" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D279" s="2">
         <f t="shared" si="4"/>
-        <v>622021</v>
+        <v>632021</v>
       </c>
       <c r="E279" s="2">
-        <v>2581.3020000000001</v>
+        <v>815.14480000000003</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
@@ -5533,14 +5550,14 @@
         <v>2022</v>
       </c>
       <c r="C280" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D280" s="2">
         <f t="shared" si="4"/>
-        <v>622022</v>
+        <v>632022</v>
       </c>
       <c r="E280" s="2">
-        <v>2864.348</v>
+        <v>899.79110000000003</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
@@ -5551,14 +5568,14 @@
         <v>2023</v>
       </c>
       <c r="C281" s="2">
-        <v>620000</v>
+        <v>630000</v>
       </c>
       <c r="D281" s="2">
         <f t="shared" si="4"/>
-        <v>622023</v>
+        <v>632023</v>
       </c>
       <c r="E281" s="2">
-        <v>3178.43</v>
+        <v>993.22720000000004</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
@@ -5569,14 +5586,14 @@
         <v>2014</v>
       </c>
       <c r="C282" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D282" s="2">
         <f t="shared" si="4"/>
-        <v>632014</v>
+        <v>642014</v>
       </c>
       <c r="E282" s="2">
-        <v>185.9736249081414</v>
+        <v>202.94843315237381</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
@@ -5587,14 +5604,14 @@
         <v>2015</v>
       </c>
       <c r="C283" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D283" s="2">
         <f t="shared" si="4"/>
-        <v>632015</v>
+        <v>642015</v>
       </c>
       <c r="E283" s="2">
-        <v>263.70749999999998</v>
+        <v>301.07459999999998</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
@@ -5605,14 +5622,14 @@
         <v>2016</v>
       </c>
       <c r="C284" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D284" s="2">
         <f t="shared" si="4"/>
-        <v>632016</v>
+        <v>642016</v>
       </c>
       <c r="E284" s="2">
-        <v>346.1474</v>
+        <v>404.08339999999998</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
@@ -5623,14 +5640,14 @@
         <v>2017</v>
       </c>
       <c r="C285" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D285" s="2">
         <f t="shared" si="4"/>
-        <v>632017</v>
+        <v>642017</v>
       </c>
       <c r="E285" s="2">
-        <v>470.05500000000001</v>
+        <v>602.89949999999999</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
@@ -5641,14 +5658,14 @@
         <v>2018</v>
       </c>
       <c r="C286" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D286" s="2">
         <f t="shared" si="4"/>
-        <v>632018</v>
+        <v>642018</v>
       </c>
       <c r="E286" s="2">
-        <v>549.56590000000006</v>
+        <v>701.61800000000005</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
@@ -5659,14 +5676,14 @@
         <v>2019</v>
       </c>
       <c r="C287" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D287" s="2">
         <f t="shared" si="4"/>
-        <v>632019</v>
+        <v>642019</v>
       </c>
       <c r="E287" s="2">
-        <v>714.80079999999998</v>
+        <v>849.2097</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
@@ -5677,14 +5694,14 @@
         <v>2020</v>
       </c>
       <c r="C288" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D288" s="2">
         <f t="shared" si="4"/>
-        <v>632020</v>
+        <v>642020</v>
       </c>
       <c r="E288" s="2">
-        <v>730.4991</v>
+        <v>907.30759999999998</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
@@ -5695,14 +5712,14 @@
         <v>2021</v>
       </c>
       <c r="C289" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D289" s="2">
         <f t="shared" si="4"/>
-        <v>632021</v>
+        <v>642021</v>
       </c>
       <c r="E289" s="2">
-        <v>815.14480000000003</v>
+        <v>1016.329</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
@@ -5713,14 +5730,14 @@
         <v>2022</v>
       </c>
       <c r="C290" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D290" s="2">
         <f t="shared" si="4"/>
-        <v>632022</v>
+        <v>642022</v>
       </c>
       <c r="E290" s="2">
-        <v>899.79110000000003</v>
+        <v>1125.3499999999999</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
@@ -5731,14 +5748,14 @@
         <v>2023</v>
       </c>
       <c r="C291" s="2">
-        <v>630000</v>
+        <v>640000</v>
       </c>
       <c r="D291" s="2">
         <f t="shared" si="4"/>
-        <v>632023</v>
+        <v>642023</v>
       </c>
       <c r="E291" s="2">
-        <v>993.22720000000004</v>
+        <v>1246.066</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
@@ -5749,14 +5766,14 @@
         <v>2014</v>
       </c>
       <c r="C292" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D292" s="2">
         <f t="shared" si="4"/>
-        <v>642014</v>
+        <v>652014</v>
       </c>
       <c r="E292" s="2">
-        <v>202.94843315237381</v>
+        <v>624.53584646890022</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
@@ -5767,14 +5784,14 @@
         <v>2015</v>
       </c>
       <c r="C293" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D293" s="2">
         <f t="shared" si="4"/>
-        <v>642015</v>
+        <v>652015</v>
       </c>
       <c r="E293" s="2">
-        <v>301.07459999999998</v>
+        <v>864.24270000000001</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
@@ -5785,14 +5802,14 @@
         <v>2016</v>
       </c>
       <c r="C294" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D294" s="2">
         <f t="shared" si="4"/>
-        <v>642016</v>
+        <v>652016</v>
       </c>
       <c r="E294" s="2">
-        <v>404.08339999999998</v>
+        <v>1179.172</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
@@ -5803,14 +5820,14 @@
         <v>2017</v>
       </c>
       <c r="C295" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D295" s="2">
         <f t="shared" si="4"/>
-        <v>642017</v>
+        <v>652017</v>
       </c>
       <c r="E295" s="2">
-        <v>602.89949999999999</v>
+        <v>1595.31</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
@@ -5821,14 +5838,14 @@
         <v>2018</v>
       </c>
       <c r="C296" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D296" s="2">
         <f t="shared" si="4"/>
-        <v>642018</v>
+        <v>652018</v>
       </c>
       <c r="E296" s="2">
-        <v>701.61800000000005</v>
+        <v>2092.7460000000001</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
@@ -5839,14 +5856,14 @@
         <v>2019</v>
       </c>
       <c r="C297" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D297" s="2">
         <f t="shared" si="4"/>
-        <v>642019</v>
+        <v>652019</v>
       </c>
       <c r="E297" s="2">
-        <v>849.2097</v>
+        <v>2739.7159999999999</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
@@ -5857,14 +5874,14 @@
         <v>2020</v>
       </c>
       <c r="C298" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D298" s="2">
         <f t="shared" si="4"/>
-        <v>642020</v>
+        <v>652020</v>
       </c>
       <c r="E298" s="2">
-        <v>907.30759999999998</v>
+        <v>2746.1669999999999</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
@@ -5875,14 +5892,14 @@
         <v>2021</v>
       </c>
       <c r="C299" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D299" s="2">
         <f t="shared" si="4"/>
-        <v>642021</v>
+        <v>652021</v>
       </c>
       <c r="E299" s="2">
-        <v>1016.329</v>
+        <v>3081.8049999999998</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
@@ -5893,14 +5910,14 @@
         <v>2022</v>
       </c>
       <c r="C300" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D300" s="2">
         <f t="shared" si="4"/>
-        <v>642022</v>
+        <v>652022</v>
       </c>
       <c r="E300" s="2">
-        <v>1125.3499999999999</v>
+        <v>3417.444</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
@@ -5911,198 +5928,18 @@
         <v>2023</v>
       </c>
       <c r="C301" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D301" s="2">
         <f t="shared" si="4"/>
-        <v>642023</v>
+        <v>652023</v>
       </c>
       <c r="E301" s="2">
-        <v>1246.066</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A302" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B302" s="2">
-        <v>2014</v>
-      </c>
-      <c r="C302" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D302" s="2">
-        <f t="shared" si="4"/>
-        <v>652014</v>
-      </c>
-      <c r="E302" s="2">
-        <v>624.53584646890022</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A303" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B303" s="2">
-        <v>2015</v>
-      </c>
-      <c r="C303" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D303" s="2">
-        <f t="shared" si="4"/>
-        <v>652015</v>
-      </c>
-      <c r="E303" s="2">
-        <v>864.24270000000001</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A304" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B304" s="2">
-        <v>2016</v>
-      </c>
-      <c r="C304" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D304" s="2">
-        <f t="shared" si="4"/>
-        <v>652016</v>
-      </c>
-      <c r="E304" s="2">
-        <v>1179.172</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B305" s="2">
-        <v>2017</v>
-      </c>
-      <c r="C305" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D305" s="2">
-        <f t="shared" si="4"/>
-        <v>652017</v>
-      </c>
-      <c r="E305" s="2">
-        <v>1595.31</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A306" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B306" s="2">
-        <v>2018</v>
-      </c>
-      <c r="C306" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D306" s="2">
-        <f t="shared" si="4"/>
-        <v>652018</v>
-      </c>
-      <c r="E306" s="2">
-        <v>2092.7460000000001</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A307" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B307" s="2">
-        <v>2019</v>
-      </c>
-      <c r="C307" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D307" s="2">
-        <f t="shared" si="4"/>
-        <v>652019</v>
-      </c>
-      <c r="E307" s="2">
-        <v>2739.7159999999999</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A308" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B308" s="2">
-        <v>2020</v>
-      </c>
-      <c r="C308" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D308" s="2">
-        <f t="shared" si="4"/>
-        <v>652020</v>
-      </c>
-      <c r="E308" s="2">
-        <v>2746.1669999999999</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A309" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B309" s="2">
-        <v>2021</v>
-      </c>
-      <c r="C309" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D309" s="2">
-        <f t="shared" si="4"/>
-        <v>652021</v>
-      </c>
-      <c r="E309" s="2">
-        <v>3081.8049999999998</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A310" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B310" s="2">
-        <v>2022</v>
-      </c>
-      <c r="C310" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D310" s="2">
-        <f t="shared" si="4"/>
-        <v>652022</v>
-      </c>
-      <c r="E310" s="2">
-        <v>3417.444</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A311" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B311" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C311" s="2">
-        <v>650000</v>
-      </c>
-      <c r="D311" s="2">
-        <f t="shared" si="4"/>
-        <v>652023</v>
-      </c>
-      <c r="E311" s="2">
         <v>3789.6370000000002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E311" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E301" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
